--- a/docs/TAPP_EPMA_filled-interp.xlsx
+++ b/docs/TAPP_EPMA_filled-interp.xlsx
@@ -6649,7 +6649,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0.02 wt%|0.02 wt%|0.05 wt%|0.02 wt%|0.02 wt%|0.02 wt%|0.06 wt%|0.01 wt%|0.03 wt%|0.03 wt%</t>
+          <t>SiO2: 0.02 wt%|MgO: 0.02 wt%|FeO: 0.05 wt%|Na2O: 0.02 wt%|Al2O3: 0.02 wt%|CaO: 0.02 wt%|MnO: 0.06 wt%|K2O: 0.01 wt%|TiO2: 0.03 wt%|Cr2O3: 0.03 wt%</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -6659,7 +6659,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>&lt;0.03 wt%|&lt;0.03 wt%|&lt;0.03 wt%|&lt;0.03 wt%|&lt;0.03 wt%|&lt;0.05–0.1 wt%|&lt;0.05–0.1 wt%|&lt;0.05–0.1 wt%|&lt;0.05–0.1 wt%|&lt;0.05–0.1 wt%|&lt;0.05–0.1 wt%|&lt;0.05–0.1 wt%</t>
+          <t>&lt;0.03 wt% for SiO2|&lt;0.03 wt% for TiO2|&lt;0.03 wt% for Al2O3|&lt;0.03 wt% for MgO|&lt;0.03 wt% for CaO|&lt;0.05–0.1 wt% for FeO|&lt;0.05–0.1 wt% for MnO|&lt;0.05–0.1 wt% for Cr2O3|&lt;0.05–0.1 wt% for NiO|&lt;0.05–0.1 wt% for Na2O|&lt;0.05–0.1 wt% for K2O|&lt;0.05–0.1 wt% for P2O5</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -6669,7 +6669,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>&lt;0.03 wt%|&lt;0.03 wt%|&lt;0.03 wt%|&lt;0.03 wt%|&lt;0.03 wt%|&lt;0.05–0.1 wt%|&lt;0.05–0.1 wt%|&lt;0.05–0.1 wt%|&lt;0.05–0.1 wt%|&lt;0.05–0.1 wt%|&lt;0.05–0.1 wt%|&lt;0.05–0.1 wt%</t>
+          <t>&lt;0.03 wt% for SiO2|&lt;0.03 wt% for TiO2|&lt;0.03 wt% for Al2O3|&lt;0.03 wt% for MgO|&lt;0.03 wt% for CaO|&lt;0.05–0.1 wt% for FeO|&lt;0.05–0.1 wt% for MnO|&lt;0.05–0.1 wt% for Cr2O3|&lt;0.05–0.1 wt% for NiO|&lt;0.05–0.1 wt% for Na2O|&lt;0.05–0.1 wt% for K2O|&lt;0.05–0.1 wt% for P2O5</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
@@ -6679,7 +6679,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>0.05 wt%|0.06 wt%|0.02 wt%|0.02 wt%|0.03 wt%|0.06 wt%|0.02 wt%|0.04 wt%|0.05 wt%|0.06 wt%</t>
+          <t>Si: 0.05 wt%|Al: 0.06 wt%|K: 0.02 wt%|Ca: 0.02 wt%|Na: 0.03 wt%|Fe: 0.06 wt%|Mg: 0.02 wt%|Ti: 0.04 wt%|Cr: 0.05 wt%|Mn: 0.06 wt%</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -6689,7 +6689,7 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>0.05 wt%|0.03–0.04 wt%|0.06–0.09 wt%|0.03–0.04 wt%|0.05 wt%|0.05 wt%|0.05 wt%|0.03–0.04 wt%|0.06–0.09 wt%|0.05 wt%|0.06–0.09 wt%|0.06–0.09 wt%|0.06–0.09 wt%|0.06–0.09 wt%</t>
+          <t>SiO2: 0.05 wt%|Al2O3: 0.03–0.04 wt%|TiO2: 0.06–0.09 wt%|K2O: 0.03–0.04 wt%|Na2O: 0.05 wt%|FeO: 0.05 wt%|MgO: 0.05 wt%|CaO: 0.03–0.04 wt%|SO2: 0.06–0.09 wt%|MnO: 0.05 wt%|Cr2O3: 0.06–0.09 wt%|NiO: 0.06–0.09 wt%|P2O5: 0.06–0.09 wt%|V2O3: 0.06–0.09 wt%</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
